--- a/SGC-CKN/Excel/33ea1258-58df-472b-859d-26265707bddb_Lô_CT-02_P1-146_D800_26-03-2026.xlsx
+++ b/SGC-CKN/Excel/33ea1258-58df-472b-859d-26265707bddb_Lô_CT-02_P1-146_D800_26-03-2026.xlsx
@@ -112,7 +112,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">16:55
@@ -122,7 +122,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha, xám ghi, xám nâu, xám vàng, TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">17:01
@@ -142,7 +142,7 @@
     <t>11</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">17:30
@@ -152,7 +152,7 @@
     <t>14</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">18:15
@@ -162,7 +162,7 @@
     <t>15</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
+    <t>Cát thô, xám vàng, xám xanh, xám nâu, KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">20:47
@@ -172,14 +172,14 @@
     <t>16</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">22:22
 26/03/2026</t>
   </si>
   <si>
-    <t>NT CA - Sợi CA - 3G02</t>
+    <t>NT chạm sỏi CĐ -36,01m</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
